--- a/data/trans_camb/CAGE_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 10,04</t>
+          <t>3,81; 10,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,4</t>
+          <t>1,47; 7,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 8,12</t>
+          <t>-0,2; 8,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,71</t>
+          <t>-1,14; 0,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,36</t>
+          <t>0,26; 4,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,4</t>
+          <t>1,72; 5,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,84</t>
+          <t>1,34; 4,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 5,49</t>
+          <t>-0,21; 5,19</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>127,72; 2603,61</t>
+          <t>97,44; 2713,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 2180,24</t>
+          <t>17,59; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,06; 2369,65</t>
+          <t>120,77; 1947,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,44; 2271,54</t>
+          <t>48,58; 1833,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 2257,36</t>
+          <t>-67,81; 2023,64</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,77</t>
+          <t>-0,72; 2,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,7</t>
+          <t>-1,92; 0,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,59</t>
+          <t>-2,79; -0,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,43</t>
+          <t>-0,39; 1,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,59</t>
+          <t>-0,82; 0,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; -0,28</t>
+          <t>-1,32; -0,3</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 387,85</t>
+          <t>-38,64; 448,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-90,06; 116,77</t>
+          <t>-87,7; 158,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,85; 416,04</t>
+          <t>-48,5; 342,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,29; 196,52</t>
+          <t>-83,55; 181,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,09</t>
+          <t>2,5; 8,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,93</t>
+          <t>0,49; 5,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,76</t>
+          <t>2,26; 6,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,29</t>
+          <t>-3,51; -0,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,03</t>
+          <t>-3,17; 0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,27</t>
+          <t>-2,23; 2,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>-2,26; 0,0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>-2,63; 0,0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,48; 0,0</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,42</t>
+          <t>-1,34; 1,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,3</t>
+          <t>-2,3; -0,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; -0,18</t>
+          <t>-2,22; -0,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,55</t>
+          <t>-1,27; 1,46</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 415,61</t>
+          <t>-100,0; 451,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3,21</t>
+          <t>-100,0; 28,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 129,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 253,78</t>
+          <t>-76,24; 267,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,53</t>
+          <t>0,49; 5,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,18</t>
+          <t>-0,44; 3,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,0</t>
+          <t>-3,23; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,0</t>
+          <t>-3,43; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 25,17</t>
+          <t>-0,86; 22,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,3</t>
+          <t>-0,6; 2,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,1</t>
+          <t>-1,31; 1,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,73</t>
+          <t>-1,01; 5,13</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-72,35; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,51</t>
+          <t>-2,56; 0,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,16</t>
+          <t>-2,23; 1,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,62</t>
+          <t>-0,92; 4,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,45; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,69</t>
+          <t>-1,77; 0,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,33</t>
+          <t>-0,52; 5,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,03</t>
+          <t>-1,85; 0,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,59</t>
+          <t>-1,66; 0,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,1</t>
+          <t>-0,1; 3,76</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-96,28; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 314,68</t>
+          <t>-100,0; 282,96</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 1420,7</t>
+          <t>-48,89; 1079,06</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,66</t>
+          <t>0,41; 2,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,8</t>
+          <t>0,88; 3,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,15</t>
+          <t>0,97; 4,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,99</t>
+          <t>0,31; 1,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,66</t>
+          <t>0,16; 4,59</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,5</t>
+          <t>0,29; 1,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,43</t>
+          <t>0,76; 2,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,83</t>
+          <t>0,5; 3,83</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 1391,67</t>
+          <t>7,59; 1850,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>63,86; 2178,34</t>
+          <t>53,5; 2131,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56,2; 2740,73</t>
+          <t>46,09; 2894,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,27; 1816,33</t>
+          <t>37,6; 2057,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>128,54; 2721,96</t>
+          <t>106,92; 2959,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>103,4; 3902,78</t>
+          <t>116,3; 3853,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,38</t>
+          <t>0,03; 2,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,95</t>
+          <t>-0,55; 1,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,58</t>
+          <t>-0,2; 2,71</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,22</t>
+          <t>-0,77; 0,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,53</t>
+          <t>-0,52; 0,54</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,9</t>
+          <t>-0,26; 4,16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,08</t>
+          <t>-0,06; 1,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,58</t>
+          <t>-0,38; 0,58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,44</t>
+          <t>0,11; 2,43</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 1267,57</t>
+          <t>-21,15; 1493,09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-80,78; 528,22</t>
+          <t>-76,02; 743,97</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 1603,36</t>
+          <t>-51,83; 1728,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 606,08</t>
+          <t>-32,89; 657,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 364,92</t>
+          <t>-69,9; 310,09</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 1151,28</t>
+          <t>-33,2; 1079,21</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,77</t>
+          <t>0,63; 1,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,21</t>
+          <t>0,16; 1,24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,35</t>
+          <t>0,74; 2,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,08</t>
+          <t>-0,4; 0,07</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,51</t>
+          <t>-0,11; 0,49</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,98</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,84</t>
+          <t>0,17; 0,78</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,75</t>
+          <t>0,11; 0,72</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,01</t>
+          <t>0,64; 1,93</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>48,48; 305,79</t>
+          <t>58,31; 310,93</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>13,79; 219,2</t>
+          <t>10,24; 200,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>72,37; 400,91</t>
+          <t>75,12; 409,43</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-88,23; 84,49</t>
+          <t>-88,11; 85,72</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 337,74</t>
+          <t>-37,4; 312,52</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>63,17; 1178,94</t>
+          <t>50,07; 1035,17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,22; 208,48</t>
+          <t>25,21; 201,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>16,83; 188,71</t>
+          <t>17,59; 189,01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>126,35; 497,5</t>
+          <t>110,68; 455,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/CAGE_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,6</t>
+          <t>3,84; 10,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,4</t>
+          <t>1,38; 7,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 8,38</t>
+          <t>-0,34; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,72</t>
+          <t>-1,16; 0,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,51</t>
+          <t>0,31; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,57; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,46</t>
+          <t>1,65; 5,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,94</t>
+          <t>1,52; 5,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,19</t>
+          <t>-0,4; 3,89</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>236,34%</t>
+          <t>177,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>224,78%</t>
+          <t>155,9%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,44; 2713,94</t>
+          <t>122,54; 2810,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,59; —</t>
+          <t>35,38; 1822,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>120,77; 1947,96</t>
+          <t>86,27; 2200,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,58; 1833,86</t>
+          <t>78,41; 2112,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,81; 2023,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,8</t>
+          <t>-0,71; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,75</t>
+          <t>-1,91; 0,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,58</t>
+          <t>-2,64; -0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,4</t>
+          <t>-0,32; 1,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,55</t>
+          <t>-0,8; 0,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,3</t>
+          <t>-1,36; -0,28</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 448,05</t>
+          <t>-50,57; 465,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,7; 158,49</t>
+          <t>-89,44; 148,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 342,13</t>
+          <t>-40,79; 387,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,55; 181,13</t>
+          <t>-81,62; 196,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,62</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,64</t>
+          <t>3,14; 9,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,41</t>
+          <t>0,47; 4,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,47</t>
+          <t>2,79; 7,65</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,22</t>
+          <t>-3,34; -0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,03</t>
+          <t>-3,13; 0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,09</t>
+          <t>-2,37; 1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,58</t>
+          <t>-1,42; 1,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,32</t>
+          <t>-2,33; -0,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; -0,24</t>
+          <t>-2,16; -0,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,46</t>
+          <t>-1,43; 1,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,0%</t>
+          <t>-28,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>-0,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,81%</t>
+          <t>-15,26%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 451,41</t>
+          <t>-100,0; 344,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,24; 267,56</t>
+          <t>-80,41; 231,85</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,53</t>
+          <t>0,54; 5,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,12</t>
+          <t>-0,44; 3,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,0</t>
+          <t>-4,01; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,0</t>
+          <t>-4,68; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 22,31</t>
+          <t>-0,81; 22,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,28</t>
+          <t>-0,49; 2,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,11</t>
+          <t>-1,25; 1,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,13</t>
+          <t>-1,02; 4,6</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>542,16%</t>
+          <t>442,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-72,35; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,51</t>
+          <t>-2,68; 0,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,18</t>
+          <t>-2,21; 1,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,49</t>
+          <t>-0,79; 4,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,0</t>
+          <t>-2,44; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,69</t>
+          <t>-1,78; 0,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,3</t>
+          <t>-0,54; 5,25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,03</t>
+          <t>-1,96; 0,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,55</t>
+          <t>-1,72; 0,57</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,76</t>
+          <t>0,02; 3,7</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184,96%</t>
+          <t>173,86%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>223,35%</t>
+          <t>219,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>208,93%</t>
+          <t>199,37%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-96,21; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 282,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 1079,06</t>
+          <t>-40,67; 1007,37</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,84</t>
+          <t>0,26; 2,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,65</t>
+          <t>0,89; 3,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,92</t>
+          <t>1,67; 7,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,78</t>
+          <t>0,3; 1,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,59</t>
+          <t>1,66; 8,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,55</t>
+          <t>0,33; 1,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,45</t>
+          <t>0,8; 2,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,83</t>
+          <t>2,4; 6,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>557,49%</t>
+          <t>810,43%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>908,79%</t>
+          <t>1755,85%</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,59; 1850,83</t>
+          <t>3,6; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>53,5; 2131,07</t>
+          <t>53,5; 2733,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46,09; 2894,57</t>
+          <t>116,23; 3476,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,6; 2057,34</t>
+          <t>12,24; 1693,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>106,92; 2959,36</t>
+          <t>120,64; 2583,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>116,3; 3853,24</t>
+          <t>392,94; 6455,58</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,93</t>
         </is>
       </c>
     </row>
@@ -2189,22 +2189,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,44</t>
+          <t>0,15; 2,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,02</t>
+          <t>-0,52; 1,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,71</t>
+          <t>-0,31; 2,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,23</t>
+          <t>-0,65; 0,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2214,22 +2214,22 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,16</t>
+          <t>-0,26; 4,29</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,1</t>
+          <t>-0,1; 1,07</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,58</t>
+          <t>-0,36; 0,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,43</t>
+          <t>0,01; 2,32</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>168,46%</t>
+          <t>161,64%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>440,57%</t>
+          <t>426,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>259,75%</t>
+          <t>250,58%</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 1493,09</t>
+          <t>-15,34; 1210,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-76,02; 743,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 1728,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 657,68</t>
+          <t>-30,63; 601,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,9; 310,09</t>
+          <t>-70,99; 305,68</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 1079,21</t>
+          <t>-28,08; 1044,43</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,73</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,79</t>
+          <t>0,56; 1,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,24</t>
+          <t>0,18; 1,2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,45</t>
+          <t>0,9; 2,54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,07</t>
+          <t>-0,42; 0,09</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,49</t>
+          <t>-0,09; 0,54</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,79; 2,85</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,78</t>
+          <t>0,2; 0,8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,72</t>
+          <t>0,11; 0,71</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,93</t>
+          <t>1,16; 2,39</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>186,74%</t>
+          <t>214,75%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>377,6%</t>
+          <t>575,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>257,9%</t>
+          <t>329,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>58,31; 310,93</t>
+          <t>55,08; 312,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10,24; 200,54</t>
+          <t>16,13; 212,68</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>75,12; 409,43</t>
+          <t>84,5; 436,34</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 85,72</t>
+          <t>-88,23; 99,41</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 312,52</t>
+          <t>-30,8; 367,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>50,07; 1035,17</t>
+          <t>143,35; 1685,86</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,21; 201,8</t>
+          <t>27,97; 197,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>17,59; 189,01</t>
+          <t>16,44; 184,63</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>110,68; 455,96</t>
+          <t>167,37; 560,9</t>
         </is>
       </c>
     </row>
